--- a/data/category_mapping.xlsx
+++ b/data/category_mapping.xlsx
@@ -1,100 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
-  <si>
-    <t>account_num</t>
-  </si>
-  <si>
-    <t>account_name</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>subcategory</t>
-  </si>
-  <si>
-    <t>הכנסות</t>
-  </si>
-  <si>
-    <t>הכנסות זקופות</t>
-  </si>
-  <si>
-    <t>סולר צמ"ה</t>
-  </si>
-  <si>
-    <t>הוצאות שכר עבודה</t>
-  </si>
-  <si>
-    <t>שכר עובדים זרים</t>
-  </si>
-  <si>
-    <t>קבלני משנה</t>
-  </si>
-  <si>
-    <t>מים וביוב</t>
-  </si>
-  <si>
-    <t>ניהול ויעוץ</t>
-  </si>
-  <si>
-    <t>הוצאות חריגות</t>
-  </si>
-  <si>
-    <t>סולר וצמ"ה</t>
-  </si>
-  <si>
-    <t>שכר עבודה</t>
-  </si>
-  <si>
-    <t>תשתיות</t>
-  </si>
-  <si>
-    <t>ניהול</t>
-  </si>
-  <si>
-    <t>זקופות</t>
-  </si>
-  <si>
-    <t>סולר</t>
-  </si>
-  <si>
-    <t>שכר ישראלי</t>
-  </si>
-  <si>
-    <t>שכר זרים</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -113,13 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -407,162 +408,1909 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>account_num</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name_keyword</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>subcategory</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B2" t="n">
         <v>927</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>הכנסות</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3" t="n">
         <v>951</v>
       </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>הכנסות</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B4" t="n">
         <v>7367</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>הכנסות</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>זקופות</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B5" t="n">
         <v>74327</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>סולר וצמ"ה</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>סולר</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B6" t="n">
         <v>7366</v>
       </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>שכר ישראלי</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B7" t="n">
         <v>74326</v>
       </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>שכר זרים</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>7368</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ביטוח לאומי</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7369</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>גמל</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7370</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>קרן השתלמות</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>7371</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>פיצויים</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>74311</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>קבלני משנה</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="n">
+        <v>74330</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ניהול ופיקוח</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ניהול/יעוץ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="n">
+        <v>74329</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ניהול ופיקוח</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>מדידה</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="n">
+        <v>74325</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ניהול ופיקוח</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>סיור ופיקוח</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" t="n">
+        <v>74315</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ניהול ופיקוח</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>פיקוח</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" t="n">
+        <v>74320</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>הובלה</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" t="n">
+        <v>74317</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>רכבים</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>סולר/בנזין/חשמל</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" t="n">
+        <v>74318</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>רכבים</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>כללי</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B20" t="n">
+        <v>74313</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>רכבים</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ביטוח/רישיון</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B21" t="n">
+        <v>74321</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>כלי צמ"ה</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B22" t="n">
+        <v>74322</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>כלי עבודה ומתכלים</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B23" t="n">
+        <v>74328</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>כללי</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B24" t="n">
+        <v>74331</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>שמנים/אוריאה</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>10</v>
+      </c>
+      <c r="B25" t="n">
+        <v>74357</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>מים/ביוב/ניקוז</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26" t="n">
+        <v>74351</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>סלילה</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>10</v>
+      </c>
+      <c r="B27" t="n">
+        <v>74344</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>אתר ותפעול</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>גידור</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>10</v>
+      </c>
+      <c r="B28" t="n">
+        <v>74398</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>אתר ותפעול</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>הקמת אתר</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>74397</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>אתר ותפעול</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>אתר שוטפות</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>10</v>
+      </c>
+      <c r="B30" t="n">
+        <v>74316</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>משרד וכלכלה</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>משרד</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>10</v>
+      </c>
+      <c r="B31" t="n">
+        <v>74323</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>משרד וכלכלה</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>כיבוד/כלכלה</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B32" t="n">
+        <v>74336</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>משרד וכלכלה</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>תקשורת</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" t="n">
+        <v>74399</v>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>הוצאות חריגות</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>10</v>
+      </c>
+      <c r="B34" t="n">
+        <v>7439957</v>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>הוצאות חריגות</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>74311</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>74310</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>74330</v>
-      </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>74399</v>
-      </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>7439957</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>12</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ביטוח לאומי</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>ביטוח לאומי</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>20</v>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>קרן השתלמות</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>קרן השתלמות</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>20</v>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>גמל פיצוי</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>פיצויים</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>20</v>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>פיצויים</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>פיצויים</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>20</v>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>גמל</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>שכר עבודה</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>גמל</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>25</v>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>סולר</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>סולר וצמ"ה</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>סולר</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>25</v>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>סולר וצמ"ה</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>דלק</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>25</v>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>בנזין</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>סולר וצמ"ה</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>בנזין</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>25</v>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>שמנים</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>שמנים/אוריאה</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>25</v>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>אוריאה</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>שמנים/אוריאה</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>30</v>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>פינוי פסולת</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>פינוי פסולת</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>35</v>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>קבלני משנה</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>קבלני משנה</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>35</v>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>קבלן משנה</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>קבלני משנה</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ניהול</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>ניהול ופיקוח</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ניהול</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>40</v>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>יעוץ</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ניהול ופיקוח</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ייעוץ</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>40</v>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>מדידה</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ניהול ופיקוח</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>מדידה</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>40</v>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>פיקוח</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ניהול ופיקוח</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>פיקוח</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>40</v>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>סיור</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ניהול ופיקוח</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>סיור</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>שוחה</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>שוחות</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>45</v>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>פודסט</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>שוחות</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>45</v>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>צינור</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>צינורות</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>45</v>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>חפירה</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>חפירה</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>45</v>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>חישוף</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>חפירה</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>45</v>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>חפור</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>חפירה</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>45</v>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>הידוק</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>מצעים</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>45</v>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>מילוי</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>מצעים</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>45</v>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>מצע</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>מצעים</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>45</v>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>סלילה</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>סלילה</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>45</v>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>אספלט</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>סלילה</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>45</v>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>מים, ביוב</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>מים/ביוב/ניקוז</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>45</v>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>מים וביוב</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>מים/ביוב/ניקוז</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>45</v>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ביוב</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>מים/ביוב/ניקוז</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>45</v>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ניקוז</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>תשתיות</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>מים/ביוב/ניקוז</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>50</v>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>רכבים</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>רכבים</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>כללי</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>50</v>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>רכב</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>רכבים</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>כללי</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>55</v>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>אחזקת כלי</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>55</v>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>אחזקה</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>55</v>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>כלי עבודה</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>כלי עבודה ומתכלים</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>55</v>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>מוסך</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>מוסך</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>55</v>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>תיקון</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>תיקונים</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>55</v>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>חלפים</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>אחזקת כלים</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>חלפים</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>60</v>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ביטוח</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ביטוחים</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>65</v>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>בטון</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>חומרים</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>בטון</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>65</v>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>חצץ</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>חומרים</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>אגרגטים</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>65</v>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>חומרים</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>חומרים</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>70</v>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>הובלה</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>הובלה</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>70</v>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>שכירות</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>שכירות ציוד</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>70</v>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>השכרה</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>שכירות ציוד</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>75</v>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>הקמת אתר</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>אתר ותפעול</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>הקמה</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>75</v>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>גידור</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>אתר ותפעול</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>גידור</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>75</v>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>אתר שוטפות</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>אתר ותפעול</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>אתר שוטפות</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>75</v>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>תקשורת</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>משרד וכלכלה</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>תקשורת</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>75</v>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>תיקשורת</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>משרד וכלכלה</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>תקשורת</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>75</v>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>משרד</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>משרד וכלכלה</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>משרד</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>75</v>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>כיבוד</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>משרד וכלכלה</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>כיבוד/כלכלה</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>75</v>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>כלכלה</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>משרד וכלכלה</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>כיבוד/כלכלה</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>80</v>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>רשויות</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>אגרות ורשויות</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>80</v>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>אגרות</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>אגרות ורשויות</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>80</v>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>אגרה</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>אגרות ורשויות</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>85</v>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>הכנסות</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>הכנסות</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>85</v>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>חיוב ספק פרויקט</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>הכנסות</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>חיוב ספק</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>חריגות</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>הוצאות חריגות</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -794,13 +2542,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAD6E44A-B5C9-4758-A1A8-BC67EA6D707D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD572033-4D43-4DBC-AFEE-B4951721409A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{16DC0E89-1C8B-4C40-BA40-81091E7D7F9D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27714560-FD87-4DD1-84F8-FEAC85E726CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C83A538-D25F-4966-9312-2889AF03AB81}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63977FEA-2099-477A-8976-33B3F37BB68D}"/>
 </file>